--- a/artfynd/A 24892-2026 artfynd.xlsx
+++ b/artfynd/A 24892-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298448</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294366</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298456</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298400</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294367</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298450</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1437,6 +1472,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298451</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1545,6 +1585,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298396</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1652,6 +1697,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294371</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1764,6 +1814,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294372</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1880,6 +1935,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298455</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1996,6 +2056,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294369</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2112,6 +2177,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298453</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2223,6 +2293,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298452</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2334,6 +2409,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298460</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2441,6 +2521,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294370</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2548,6 +2633,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298404</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2656,6 +2746,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298392</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2763,6 +2858,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294368</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2874,8 +2974,35 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298454</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24892-2026 artfynd.xlsx
+++ b/artfynd/A 24892-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135298448</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135294366</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135298456</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>135298400</v>
       </c>
       <c r="B5" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>135294367</v>
       </c>
       <c r="B6" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>135298450</v>
       </c>
       <c r="B7" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>135298451</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>135298396</v>
       </c>
       <c r="B9" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>135294371</v>
       </c>
       <c r="B10" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>135294372</v>
       </c>
       <c r="B11" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>135298455</v>
       </c>
       <c r="B12" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>135294369</v>
       </c>
       <c r="B13" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>135298453</v>
       </c>
       <c r="B14" t="n">
-        <v>56706</v>
+        <v>56711</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>135298452</v>
       </c>
       <c r="B15" t="n">
-        <v>58839</v>
+        <v>58844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>135298460</v>
       </c>
       <c r="B16" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>135294370</v>
       </c>
       <c r="B17" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>135298404</v>
       </c>
       <c r="B18" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>135298392</v>
       </c>
       <c r="B19" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>135294368</v>
       </c>
       <c r="B20" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>135298454</v>
       </c>
       <c r="B21" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24892-2026 artfynd.xlsx
+++ b/artfynd/A 24892-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135298448</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135294366</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135298456</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>135298400</v>
       </c>
       <c r="B5" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>135294367</v>
       </c>
       <c r="B6" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>135298450</v>
       </c>
       <c r="B7" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>135298451</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>135298396</v>
       </c>
       <c r="B9" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>135294371</v>
       </c>
       <c r="B10" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>135294370</v>
       </c>
       <c r="B17" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>135298404</v>
       </c>
       <c r="B18" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>135298392</v>
       </c>
       <c r="B19" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>135294368</v>
       </c>
       <c r="B20" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>135298454</v>
       </c>
       <c r="B21" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24892-2026 artfynd.xlsx
+++ b/artfynd/A 24892-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135298448</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>135298400</v>
       </c>
       <c r="B5" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>135294367</v>
       </c>
       <c r="B6" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>135298450</v>
       </c>
       <c r="B7" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>135294370</v>
       </c>
       <c r="B17" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
